--- a/SuppXLS/Scen_UC_RENHEAT_MANHEAT_20_50.xlsx
+++ b/SuppXLS/Scen_UC_RENHEAT_MANHEAT_20_50.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83D59405-8D32-4532-8D97-1860C1AC9C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638A490F-3FA8-4F95-8887-FB2D57A24106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
-    <sheet name="RENHEAT_MANHEAT_10_25" sheetId="1" r:id="rId1"/>
+    <sheet name="RENHEAT_MANHEAT_20_50" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/SuppXLS/Scen_UC_RENHEAT_MANHEAT_20_50.xlsx
+++ b/SuppXLS/Scen_UC_RENHEAT_MANHEAT_20_50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638A490F-3FA8-4F95-8887-FB2D57A24106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFF5D71-5340-4F89-8567-5A3CC67B609E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>UC - Each Region/Period</t>
   </si>
@@ -95,18 +95,9 @@
     <t>AllRegions</t>
   </si>
   <si>
-    <t>UC_COMPRD</t>
-  </si>
-  <si>
-    <t>DMD</t>
-  </si>
-  <si>
     <t>MANHEAT</t>
   </si>
   <si>
-    <t>RENHEAT</t>
-  </si>
-  <si>
     <t>UC_RENHEAT_MANHEAT_20_50</t>
   </si>
   <si>
@@ -114,6 +105,9 @@
   </si>
   <si>
     <t>Minimum RENHEAT penetration for process heat</t>
+  </si>
+  <si>
+    <t>RNWHEAT</t>
   </si>
 </sst>
 </file>
@@ -714,19 +708,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
       <c r="D6" s="8"/>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
       <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
         <v>19</v>
       </c>
       <c r="I6">
@@ -748,24 +736,18 @@
         <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
       <c r="D7" s="8"/>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
       <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" t="s">
         <v>19</v>
       </c>
       <c r="I7">
@@ -787,7 +769,7 @@
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
